--- a/artfynd/A 12690-2026 artfynd.xlsx
+++ b/artfynd/A 12690-2026 artfynd.xlsx
@@ -678,16 +678,11 @@
         <v>80431303</v>
       </c>
       <c r="B2" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -700,12 +695,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -726,10 +721,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>474787.4863205055</v>
+        <v>474787</v>
       </c>
       <c r="R2" t="n">
-        <v>6580384.448966224</v>
+        <v>6580384</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,19 +754,9 @@
           <t>2019-10-13</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-10-13</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
